--- a/autoast/auto_ast_v3_Breville_folium_maps/jobs_template.xlsx
+++ b/autoast/auto_ast_v3_Breville_folium_maps/jobs_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Northeast</t>
   </si>
@@ -95,13 +95,13 @@
     <t>\\spatialfiles.bcgov\srm\gss\authorizations\land\2025\thompson_okanagan\3413639\Shapefile\3413639.shp</t>
   </si>
   <si>
-    <t/>
+    <t>C:\Users\CSOSTAD\Desktop\ast test</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
   <si>
     <t>True</t>
-  </si>
-  <si>
-    <t>False</t>
   </si>
 </sst>
 </file>
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,85 +201,46 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -612,210 +573,184 @@
   <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="23.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="138.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="23.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="27" width="17.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="110.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="28" width="29.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="28" width="26.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="29" width="29.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="29" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="28" width="21.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="28" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="8" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="8" width="11.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="23.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="138.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="23.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="17.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="110.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="26.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="16" width="29.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="16" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="16" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="16" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="14.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="13"/>
+      <c r="O1" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="13"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="13"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="9"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="13"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="21" t="s">
-        <v>26</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -836,9 +771,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="27.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="27.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -860,42 +795,42 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2"/>
